--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AA9C8E4-DB89-49DD-96F4-BADC22CF9879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3326975B-2F3C-412E-8704-9B71BD1354D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{BB19E4B8-DADD-49FE-854E-B2096118BFB9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{EC551D43-73B9-4172-8F4E-9160881069D4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE961539-C3D7-4565-BD4D-9B31C8B28060}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0612957C-47E2-44E8-AFAB-BB500027FED0}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3326975B-2F3C-412E-8704-9B71BD1354D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0483687B-30C1-4051-8745-995BBF99A2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{EC551D43-73B9-4172-8F4E-9160881069D4}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{0E598E67-E19F-47D3-874A-F499CBF03568}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0612957C-47E2-44E8-AFAB-BB500027FED0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54198F4E-35D0-4BD4-B6BE-3C520C02A88E}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0483687B-30C1-4051-8745-995BBF99A2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF9C6EC6-1347-4899-904C-A1C5B5F3F05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{0E598E67-E19F-47D3-874A-F499CBF03568}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{0AB0FDF5-2268-4378-B334-A46A25C1FC98}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54198F4E-35D0-4BD4-B6BE-3C520C02A88E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B63B0E9-4644-45E7-9DEC-5AE2D9011F76}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF9C6EC6-1347-4899-904C-A1C5B5F3F05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A90F77E8-5E5F-4883-9CA8-4AFEF23FA530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{0AB0FDF5-2268-4378-B334-A46A25C1FC98}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{9C48759F-CB9E-4724-A71F-144EA61CF480}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B63B0E9-4644-45E7-9DEC-5AE2D9011F76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEFDC64-A722-414B-B602-9EA0364D6262}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A90F77E8-5E5F-4883-9CA8-4AFEF23FA530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E672D2CE-E3D5-467C-825A-181FBDC9F937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{9C48759F-CB9E-4724-A71F-144EA61CF480}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{F920A1C2-8FF3-433F-9277-726E94D50534}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEFDC64-A722-414B-B602-9EA0364D6262}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{027C3AEF-5306-44BD-BB0F-E80070DA45AD}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E672D2CE-E3D5-467C-825A-181FBDC9F937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8751AC36-8FD1-45E6-BCC1-A2B9ADF933FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{F920A1C2-8FF3-433F-9277-726E94D50534}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{363F20FC-1B76-4617-AF5D-164B33D83598}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{027C3AEF-5306-44BD-BB0F-E80070DA45AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF30C09C-4AB9-4F63-A350-024D202E3AB9}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8751AC36-8FD1-45E6-BCC1-A2B9ADF933FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{875C308D-130C-4FFE-A689-0D01FADF9523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{363F20FC-1B76-4617-AF5D-164B33D83598}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{8AB0F3FA-48BF-4317-B13E-67EB3829F3B2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF30C09C-4AB9-4F63-A350-024D202E3AB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A592F893-B28B-46F4-9E0F-CCA588B308C1}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{875C308D-130C-4FFE-A689-0D01FADF9523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{904243B2-4008-4FD1-8D89-D23B51E7965C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{8AB0F3FA-48BF-4317-B13E-67EB3829F3B2}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{6EA1E893-CD35-4A77-949F-99445BAE00B9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A592F893-B28B-46F4-9E0F-CCA588B308C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1131ADE3-4272-4CC2-9260-10479CB425DB}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{904243B2-4008-4FD1-8D89-D23B51E7965C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76AA56E-F94B-441F-B0FB-E6D5C19652A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{6EA1E893-CD35-4A77-949F-99445BAE00B9}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{AF9A2169-0E14-4E8B-B462-F3617F96E702}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1131ADE3-4272-4CC2-9260-10479CB425DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF89F45-D8AE-401C-96A5-2D89105E42E8}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
